--- a/automated_message/schedule.xlsx
+++ b/automated_message/schedule.xlsx
@@ -1,20 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29711"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ronpa\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="35" documentId="13_ncr:1_{AF15AE7B-E492-4F06-AB66-41DF61446A7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{65E8D2FA-2A35-4D99-870A-C22C6509834E}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView xWindow="12710" yWindow="0" windowWidth="12980" windowHeight="13770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet r:id="rId1" sheetId="1" name="Sheet1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="32">
   <si>
     <t>name</t>
   </si>
@@ -31,24 +53,92 @@
     <t>location</t>
   </si>
   <si>
+    <t>registration</t>
+  </si>
+  <si>
+    <t>Main Lobby</t>
+  </si>
+  <si>
+    <t>opening ceremonies</t>
+  </si>
+  <si>
+    <t>PGCLL 127</t>
+  </si>
+  <si>
+    <t>lunch</t>
+  </si>
+  <si>
+    <t>go engineering workshop</t>
+  </si>
+  <si>
+    <t>PGCLL 124</t>
+  </si>
+  <si>
+    <t>chill room</t>
+  </si>
+  <si>
+    <t>PGCLL B131</t>
+  </si>
+  <si>
+    <t>rendering workshop</t>
+  </si>
+  <si>
+    <t>sponsorship fair</t>
+  </si>
+  <si>
+    <t>Basement Lobby</t>
+  </si>
+  <si>
+    <t>blind CAD challenge</t>
+  </si>
+  <si>
+    <t>therapy dogs</t>
+  </si>
+  <si>
+    <t>PGCLL M24</t>
+  </si>
+  <si>
+    <t>dinner</t>
+  </si>
+  <si>
+    <t>duo CAD challenge</t>
+  </si>
+  <si>
+    <t>how to pitch workshop</t>
+  </si>
+  <si>
+    <t>gartic CAD challenge</t>
+  </si>
+  <si>
+    <t>rapid pitch competition</t>
+  </si>
+  <si>
+    <t>late night snacks</t>
+  </si>
+  <si>
+    <t>gaming tournament</t>
+  </si>
+  <si>
+    <t>PGCLL M21</t>
+  </si>
+  <si>
     <t>karaoke</t>
   </si>
   <si>
-    <t>PG M128</t>
-  </si>
-  <si>
-    <t>dinner</t>
-  </si>
-  <si>
-    <t>PG 127</t>
+    <t>breakfast</t>
+  </si>
+  <si>
+    <t>photobooth</t>
+  </si>
+  <si>
+    <t>closing ceremonies</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -90,50 +180,31 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="14" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="20" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="14" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="20" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="14" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="20" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="19" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0" name="Normal"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -144,10 +215,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="0E2841"/>
@@ -185,71 +256,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Times New Roman" script="Arab"/>
-        <a:font typeface="Times New Roman" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="MoolBoran" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Times New Roman" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Arial" script="Arab"/>
-        <a:font typeface="Arial" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="DaunPenh" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Arial" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -277,7 +348,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -300,11 +371,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -313,13 +384,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -329,7 +400,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -338,7 +409,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -347,7 +418,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -355,10 +426,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot rev="0" lon="0" lat="0"/>
+              <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
-              <a:rot rev="1200000" lon="0" lat="0"/>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -423,72 +494,685 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="9" width="10.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="72.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="2">
-        <v>46031</v>
-      </c>
-      <c r="C2" s="3">
-        <v>46023.95763888889</v>
-      </c>
-      <c r="D2" s="4">
-        <v>5</v>
-      </c>
-      <c r="E2" s="1" t="s">
+      <c r="B2" s="1">
+        <v>46039</v>
+      </c>
+      <c r="C2" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="D2" s="3">
+        <v>30</v>
+      </c>
+      <c r="E2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:5" ht="18.75" customHeight="1">
+      <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="5">
-        <v>46031</v>
-      </c>
-      <c r="C3" s="6">
-        <v>46023.961805555555</v>
-      </c>
-      <c r="D3" s="7">
+      <c r="B3" s="1">
+        <v>46039</v>
+      </c>
+      <c r="C3" s="5">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D3" s="4">
+        <v>15</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1">
+        <v>46039</v>
+      </c>
+      <c r="C4" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="D4" s="3">
+        <v>30</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="1">
+        <v>46039</v>
+      </c>
+      <c r="C5" s="2">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="D5" s="3">
         <v>20</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="1">
+        <v>46039</v>
+      </c>
+      <c r="C6" s="2">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D6" s="3">
+        <v>15</v>
+      </c>
+      <c r="E6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="15">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1">
+        <v>46039</v>
+      </c>
+      <c r="C7" s="2">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="D7" s="3">
+        <v>20</v>
+      </c>
+      <c r="E7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="15">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="1">
+        <v>46039</v>
+      </c>
+      <c r="C8" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="D8" s="3">
+        <v>30</v>
+      </c>
+      <c r="E8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="15">
+      <c r="A9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="1">
+        <v>46039</v>
+      </c>
+      <c r="C9" s="2">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="D9" s="3">
+        <v>20</v>
+      </c>
+      <c r="E9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="15">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="1">
+        <v>46039</v>
+      </c>
+      <c r="C10" s="2">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="D10" s="3">
+        <v>20</v>
+      </c>
+      <c r="E10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="15">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="1">
+        <v>46039</v>
+      </c>
+      <c r="C11" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="D11" s="3">
+        <v>30</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="15">
+      <c r="A12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="1">
+        <v>46039</v>
+      </c>
+      <c r="C12" s="2">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D12" s="3">
+        <v>20</v>
+      </c>
+      <c r="E12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="15">
+      <c r="A13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="1">
+        <v>46039</v>
+      </c>
+      <c r="C13" s="2">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="D13" s="3">
+        <v>20</v>
+      </c>
+      <c r="E13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="15">
+      <c r="A14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="1">
+        <v>46039</v>
+      </c>
+      <c r="C14" s="2">
+        <v>0.875</v>
+      </c>
+      <c r="D14" s="3">
+        <v>20</v>
+      </c>
+      <c r="E14" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="15">
+      <c r="A15" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" s="1">
+        <v>46039</v>
+      </c>
+      <c r="C15" s="2">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="D15" s="3">
+        <v>20</v>
+      </c>
+      <c r="E15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="15">
+      <c r="A16" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="1">
+        <v>46039</v>
+      </c>
+      <c r="C16" s="2">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="D16" s="3">
+        <v>15</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="15">
+      <c r="A17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="1">
+        <v>46039</v>
+      </c>
+      <c r="C17" s="2">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="D17" s="3">
+        <v>30</v>
+      </c>
+      <c r="E17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="15">
+      <c r="A18" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" s="1">
+        <v>46040</v>
+      </c>
+      <c r="C18" s="2">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="D18" s="3">
+        <v>30</v>
+      </c>
+      <c r="E18" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="15">
+      <c r="A19" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" s="1">
+        <v>46040</v>
+      </c>
+      <c r="C19" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D19" s="3">
+        <v>30</v>
+      </c>
+      <c r="E19" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="15">
+      <c r="A20" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="1">
+        <v>46040</v>
+      </c>
+      <c r="C20" s="2">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="D20" s="3">
+        <v>30</v>
+      </c>
+      <c r="E20" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="15">
+      <c r="A21" t="s">
+        <v>12</v>
+      </c>
+      <c r="B21" s="1">
+        <v>46040</v>
+      </c>
+      <c r="C21" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="D21" s="3">
+        <v>20</v>
+      </c>
+      <c r="E21" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="15">
+      <c r="A22" t="s">
+        <v>30</v>
+      </c>
+      <c r="B22" s="1">
+        <v>46040</v>
+      </c>
+      <c r="C22" s="2">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="D22" s="3">
+        <v>20</v>
+      </c>
+      <c r="E22" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="15">
+      <c r="A23" t="s">
+        <v>31</v>
+      </c>
+      <c r="B23" s="1">
+        <v>46040</v>
+      </c>
+      <c r="C23" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="D23" s="3">
+        <v>20</v>
+      </c>
+      <c r="E23" t="s">
         <v>8</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101000D4BF58F673F684CBFCA68DDBB9CB6DB" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c1033dc7e47c216193ad0b15a78325be">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="0c035b3a-2242-40e9-b051-410d967b3bee" xmlns:ns3="ce13748c-e217-42e0-bd93-9c0f85beefb8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="435b4a73179c65970787b7eb4511425f" ns2:_="" ns3:_="">
+    <xsd:import namespace="0c035b3a-2242-40e9-b051-410d967b3bee"/>
+    <xsd:import namespace="ce13748c-e217-42e0-bd93-9c0f85beefb8"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="0c035b3a-2242-40e9-b051-410d967b3bee" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="12" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="13" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="14" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="15" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="17" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="a073764d-e844-48d8-8cbc-d63b9d952867" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="19" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="22" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceBillingMetadata" ma:index="23" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ce13748c-e217-42e0-bd93-9c0f85beefb8" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="18" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{86fd3912-9369-4af6-8ffd-c5f703fe7f0f}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="ce13748c-e217-42e0-bd93-9c0f85beefb8">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithUsers" ma:index="20" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="21" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="ce13748c-e217-42e0-bd93-9c0f85beefb8" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="0c035b3a-2242-40e9-b051-410d967b3bee">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E080134C-2F2F-4173-9AF2-60DC32EA27AD}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06A7B2A0-9CEE-422E-B6A6-C4BECB802467}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C43EC343-635E-4E59-9648-77EE8E34610E}"/>
 </file>
--- a/automated_message/schedule.xlsx
+++ b/automated_message/schedule.xlsx
@@ -570,7 +570,7 @@
         <v>46039</v>
       </c>
       <c r="C4" s="3">
-        <v>1.5</v>
+        <v>46023.458333333336</v>
       </c>
       <c r="D4" s="4">
         <v>30</v>

--- a/automated_message/schedule.xlsx
+++ b/automated_message/schedule.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="33">
   <si>
     <t>name</t>
   </si>
@@ -38,6 +38,9 @@
   </si>
   <si>
     <t>opening ceremonies</t>
+  </si>
+  <si>
+    <t>5:00</t>
   </si>
   <si>
     <t>PGCLL 127</t>
@@ -536,7 +539,7 @@
         <v>46039</v>
       </c>
       <c r="C2" s="3">
-        <v>1.375</v>
+        <v>46023.166666666664</v>
       </c>
       <c r="D2" s="4">
         <v>30</v>
@@ -552,354 +555,354 @@
       <c r="B3" s="2">
         <v>46039</v>
       </c>
-      <c r="C3" s="5">
-        <v>1.4166666666666667</v>
+      <c r="C3" s="5" t="s">
+        <v>8</v>
       </c>
       <c r="D3" s="6">
         <v>15</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="2">
         <v>46039</v>
       </c>
       <c r="C4" s="3">
-        <v>46023.458333333336</v>
+        <v>46023.291666666664</v>
       </c>
       <c r="D4" s="4">
         <v>30</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5" s="2">
         <v>46039</v>
       </c>
       <c r="C5" s="3">
-        <v>1.5416666666666665</v>
+        <v>46023.333333333336</v>
       </c>
       <c r="D5" s="4">
         <v>20</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B6" s="2">
         <v>46039</v>
       </c>
       <c r="C6" s="3">
-        <v>1.5833333333333335</v>
+        <v>46023.375</v>
       </c>
       <c r="D6" s="4">
         <v>15</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B7" s="2">
         <v>46039</v>
       </c>
       <c r="C7" s="3">
-        <v>1.6041666666666665</v>
+        <v>46023.395833333336</v>
       </c>
       <c r="D7" s="4">
         <v>20</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B8" s="2">
         <v>46039</v>
       </c>
       <c r="C8" s="3">
-        <v>1.625</v>
+        <v>46023.416666666664</v>
       </c>
       <c r="D8" s="4">
         <v>30</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B9" s="2">
         <v>46039</v>
       </c>
       <c r="C9" s="3">
-        <v>1.7083333333333335</v>
+        <v>46023</v>
       </c>
       <c r="D9" s="4">
         <v>20</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B10" s="2">
         <v>46039</v>
       </c>
       <c r="C10" s="3">
-        <v>1.7291666666666665</v>
+        <v>46023.020833333336</v>
       </c>
       <c r="D10" s="4">
         <v>20</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B11" s="2">
         <v>46039</v>
       </c>
       <c r="C11" s="3">
-        <v>1.75</v>
+        <v>46023.541666666664</v>
       </c>
       <c r="D11" s="4">
         <v>30</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" s="2">
         <v>46039</v>
       </c>
       <c r="C12" s="3">
-        <v>1.7916666666666665</v>
+        <v>46023.583333333336</v>
       </c>
       <c r="D12" s="4">
         <v>20</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13" s="2">
         <v>46039</v>
       </c>
       <c r="C13" s="3">
-        <v>1.8333333333333335</v>
+        <v>46023.625</v>
       </c>
       <c r="D13" s="4">
         <v>20</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B14" s="2">
         <v>46039</v>
       </c>
       <c r="C14" s="3">
-        <v>1.875</v>
+        <v>46023.666666666664</v>
       </c>
       <c r="D14" s="4">
         <v>20</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B15" s="2">
         <v>46039</v>
       </c>
       <c r="C15" s="3">
-        <v>1.8958333333333335</v>
+        <v>46023.6875</v>
       </c>
       <c r="D15" s="4">
         <v>20</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
       <c r="A16" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B16" s="2">
         <v>46039</v>
       </c>
       <c r="C16" s="3">
-        <v>1.9583333333333335</v>
+        <v>46023.75</v>
       </c>
       <c r="D16" s="4">
         <v>15</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B17" s="2">
         <v>46039</v>
       </c>
       <c r="C17" s="3">
-        <v>1.9583333333333335</v>
+        <v>46023.75</v>
       </c>
       <c r="D17" s="4">
         <v>30</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B18" s="2">
-        <v>46040</v>
+        <v>46039</v>
       </c>
       <c r="C18" s="3">
-        <v>1.0833333333333333</v>
+        <v>46023.875</v>
       </c>
       <c r="D18" s="4">
         <v>30</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B19" s="2">
         <v>46040</v>
       </c>
       <c r="C19" s="3">
-        <v>1.3333333333333333</v>
+        <v>46023.125</v>
       </c>
       <c r="D19" s="4">
         <v>30</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
       <c r="A20" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B20" s="2">
         <v>46040</v>
       </c>
       <c r="C20" s="3">
-        <v>1.4791666666666667</v>
+        <v>46023.270833333336</v>
       </c>
       <c r="D20" s="4">
         <v>30</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
       <c r="A21" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B21" s="2">
         <v>46040</v>
       </c>
       <c r="C21" s="3">
-        <v>1.5</v>
+        <v>46023.291666666664</v>
       </c>
       <c r="D21" s="4">
         <v>20</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
       <c r="A22" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B22" s="2">
         <v>46040</v>
       </c>
       <c r="C22" s="3">
-        <v>1.5416666666666665</v>
+        <v>46023.333333333336</v>
       </c>
       <c r="D22" s="4">
         <v>20</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
       <c r="A23" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B23" s="2">
         <v>46040</v>
       </c>
       <c r="C23" s="3">
-        <v>1.6875</v>
+        <v>46023.479166666664</v>
       </c>
       <c r="D23" s="4">
         <v>20</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/automated_message/schedule.xlsx
+++ b/automated_message/schedule.xlsx
@@ -40,7 +40,7 @@
     <t>opening ceremonies</t>
   </si>
   <si>
-    <t>5:00</t>
+    <t>14:00</t>
   </si>
   <si>
     <t>PGCLL 127</t>
@@ -539,7 +539,7 @@
         <v>46039</v>
       </c>
       <c r="C2" s="3">
-        <v>46023.166666666664</v>
+        <v>46023.583333333336</v>
       </c>
       <c r="D2" s="4">
         <v>30</v>
@@ -573,7 +573,7 @@
         <v>46039</v>
       </c>
       <c r="C4" s="3">
-        <v>46023.291666666664</v>
+        <v>46023.708333333336</v>
       </c>
       <c r="D4" s="4">
         <v>30</v>
@@ -590,7 +590,7 @@
         <v>46039</v>
       </c>
       <c r="C5" s="3">
-        <v>46023.333333333336</v>
+        <v>46023.75</v>
       </c>
       <c r="D5" s="4">
         <v>20</v>
@@ -607,7 +607,7 @@
         <v>46039</v>
       </c>
       <c r="C6" s="3">
-        <v>46023.375</v>
+        <v>46023.791666666664</v>
       </c>
       <c r="D6" s="4">
         <v>15</v>
@@ -624,7 +624,7 @@
         <v>46039</v>
       </c>
       <c r="C7" s="3">
-        <v>46023.395833333336</v>
+        <v>46023.8125</v>
       </c>
       <c r="D7" s="4">
         <v>20</v>
@@ -641,7 +641,7 @@
         <v>46039</v>
       </c>
       <c r="C8" s="3">
-        <v>46023.416666666664</v>
+        <v>46023.833333333336</v>
       </c>
       <c r="D8" s="4">
         <v>30</v>
@@ -658,7 +658,7 @@
         <v>46039</v>
       </c>
       <c r="C9" s="3">
-        <v>46023</v>
+        <v>46023.916666666664</v>
       </c>
       <c r="D9" s="4">
         <v>20</v>
@@ -675,7 +675,7 @@
         <v>46039</v>
       </c>
       <c r="C10" s="3">
-        <v>46023.020833333336</v>
+        <v>46023.9375</v>
       </c>
       <c r="D10" s="4">
         <v>20</v>
@@ -692,7 +692,7 @@
         <v>46039</v>
       </c>
       <c r="C11" s="3">
-        <v>46023.541666666664</v>
+        <v>46023.958333333336</v>
       </c>
       <c r="D11" s="4">
         <v>30</v>
@@ -706,10 +706,10 @@
         <v>22</v>
       </c>
       <c r="B12" s="2">
-        <v>46039</v>
+        <v>46040</v>
       </c>
       <c r="C12" s="3">
-        <v>46023.583333333336</v>
+        <v>46023</v>
       </c>
       <c r="D12" s="4">
         <v>20</v>
@@ -723,10 +723,10 @@
         <v>23</v>
       </c>
       <c r="B13" s="2">
-        <v>46039</v>
+        <v>46040</v>
       </c>
       <c r="C13" s="3">
-        <v>46023.625</v>
+        <v>46023.041666666664</v>
       </c>
       <c r="D13" s="4">
         <v>20</v>
@@ -740,10 +740,10 @@
         <v>24</v>
       </c>
       <c r="B14" s="2">
-        <v>46039</v>
+        <v>46040</v>
       </c>
       <c r="C14" s="3">
-        <v>46023.666666666664</v>
+        <v>46023.083333333336</v>
       </c>
       <c r="D14" s="4">
         <v>20</v>
@@ -757,10 +757,10 @@
         <v>25</v>
       </c>
       <c r="B15" s="2">
-        <v>46039</v>
+        <v>46040</v>
       </c>
       <c r="C15" s="3">
-        <v>46023.6875</v>
+        <v>46023.104166666664</v>
       </c>
       <c r="D15" s="4">
         <v>20</v>
@@ -774,10 +774,10 @@
         <v>26</v>
       </c>
       <c r="B16" s="2">
-        <v>46039</v>
+        <v>46040</v>
       </c>
       <c r="C16" s="3">
-        <v>46023.75</v>
+        <v>46023.166666666664</v>
       </c>
       <c r="D16" s="4">
         <v>15</v>
@@ -791,10 +791,10 @@
         <v>27</v>
       </c>
       <c r="B17" s="2">
-        <v>46039</v>
+        <v>46040</v>
       </c>
       <c r="C17" s="3">
-        <v>46023.75</v>
+        <v>46023.166666666664</v>
       </c>
       <c r="D17" s="4">
         <v>30</v>
@@ -808,10 +808,10 @@
         <v>29</v>
       </c>
       <c r="B18" s="2">
-        <v>46039</v>
+        <v>46040</v>
       </c>
       <c r="C18" s="3">
-        <v>46023.875</v>
+        <v>46023.291666666664</v>
       </c>
       <c r="D18" s="4">
         <v>30</v>
@@ -828,7 +828,7 @@
         <v>46040</v>
       </c>
       <c r="C19" s="3">
-        <v>46023.125</v>
+        <v>46023.541666666664</v>
       </c>
       <c r="D19" s="4">
         <v>30</v>
@@ -845,7 +845,7 @@
         <v>46040</v>
       </c>
       <c r="C20" s="3">
-        <v>46023.270833333336</v>
+        <v>46023.6875</v>
       </c>
       <c r="D20" s="4">
         <v>30</v>
@@ -862,7 +862,7 @@
         <v>46040</v>
       </c>
       <c r="C21" s="3">
-        <v>46023.291666666664</v>
+        <v>46023.708333333336</v>
       </c>
       <c r="D21" s="4">
         <v>20</v>
@@ -879,7 +879,7 @@
         <v>46040</v>
       </c>
       <c r="C22" s="3">
-        <v>46023.333333333336</v>
+        <v>46023.75</v>
       </c>
       <c r="D22" s="4">
         <v>20</v>
@@ -896,7 +896,7 @@
         <v>46040</v>
       </c>
       <c r="C23" s="3">
-        <v>46023.479166666664</v>
+        <v>46023.895833333336</v>
       </c>
       <c r="D23" s="4">
         <v>20</v>
